--- a/docs/deploy-evidence/2026-09-25-matbjlzc-demo/最终匹配结果-演示.xlsx
+++ b/docs/deploy-evidence/2026-09-25-matbjlzc-demo/最终匹配结果-演示.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="D6" s="4">
-        <v>46290.9918011925</v>
+        <v>46292.52814669321</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2 秒</t>
+          <t>1 秒</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="D7" s="4">
-        <v>46290.99182027054</v>
+        <v>46292.52815868007</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <v>46290.99182580402</v>
+        <v>46292.52817138082</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D3" s="10">
-        <v>87.3976</v>
+        <v>87.4525</v>
       </c>
       <c r="E3" s="3">
         <v>2</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="H3" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D4" s="10">
-        <v>83.2246</v>
+        <v>83.20180000000001</v>
       </c>
       <c r="E4" s="3">
         <v>3</v>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="H4" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D5" s="10">
-        <v>81.456</v>
+        <v>81.4563</v>
       </c>
       <c r="E5" s="3">
         <v>4</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="H5" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D6" s="10">
-        <v>83.22620000000001</v>
+        <v>83.2371</v>
       </c>
       <c r="E6" s="3">
         <v>5</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="H6" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="D7" s="10">
-        <v>88.2225</v>
+        <v>88.1905</v>
       </c>
       <c r="E7" s="3">
         <v>6</v>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="H7" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="D8" s="10">
-        <v>80.224</v>
+        <v>80.22369999999999</v>
       </c>
       <c r="E8" s="3">
         <v>7</v>
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="H8" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D9" s="10">
-        <v>62.9728</v>
+        <v>63.0171</v>
       </c>
       <c r="E9" s="3">
         <v>8</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="H9" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="D10" s="10">
-        <v>79.96729999999999</v>
+        <v>79.967</v>
       </c>
       <c r="E10" s="3">
         <v>9</v>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="H10" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="D11" s="10">
-        <v>90.2171</v>
+        <v>90.17610000000001</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="H11" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <v>71.2756</v>
+        <v>71.2753</v>
       </c>
       <c r="E12" s="3">
         <v>11</v>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="H12" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <v>75.1172</v>
+        <v>75.1169</v>
       </c>
       <c r="E13" s="3">
         <v>12</v>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="H13" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="D14" s="10">
-        <v>76.4391</v>
+        <v>76.386</v>
       </c>
       <c r="E14" s="3">
         <v>13</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="H14" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D15" s="10">
-        <v>81.53879999999999</v>
+        <v>81.54640000000001</v>
       </c>
       <c r="E15" s="3">
         <v>14</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="H15" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="D16" s="10">
-        <v>83.0355</v>
+        <v>83.036</v>
       </c>
       <c r="E16" s="3">
         <v>15</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="H16" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="D17" s="10">
-        <v>76.2634</v>
+        <v>76.3137</v>
       </c>
       <c r="E17" s="3">
         <v>16</v>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="H17" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="D18" s="10">
-        <v>49.6548</v>
+        <v>49.6748</v>
       </c>
       <c r="E18" s="3">
         <v>13</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="H18" s="4">
-        <v>46290.99182502231</v>
+        <v>46292.52817064675</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="D19" s="10">
-        <v>38.8251</v>
+        <v>38.9282</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="inlineStr">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D20" s="10">
-        <v>48.4937</v>
+        <v>48.4922</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="inlineStr">
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="H20" s="4">
-        <v>46290.991825282</v>
+        <v>46292.52817096916</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="D22" s="10">
-        <v>58.4443</v>
+        <v>58.4431</v>
       </c>
       <c r="E22" s="3">
         <v>47</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="H22" s="4">
-        <v>46290.99181991853</v>
+        <v>46292.52815840205</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="E3" s="10">
-        <v>87.3976</v>
+        <v>87.4525</v>
       </c>
       <c r="F3" s="3">
         <v>2</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="E4" s="10">
-        <v>68.2567</v>
+        <v>68.2479</v>
       </c>
       <c r="F4" s="3">
         <v>3</v>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="E5" s="10">
-        <v>54.2335</v>
+        <v>54.2354</v>
       </c>
       <c r="F5" s="3">
         <v>4</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="E6" s="10">
-        <v>54.1333</v>
+        <v>54.1352</v>
       </c>
       <c r="F6" s="3">
         <v>11</v>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="E7" s="10">
-        <v>49.8914</v>
+        <v>49.8869</v>
       </c>
       <c r="F7" s="3">
         <v>12</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="E8" s="10">
-        <v>83.2246</v>
+        <v>83.20180000000001</v>
       </c>
       <c r="F8" s="3">
         <v>3</v>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="E9" s="10">
-        <v>61.8315</v>
+        <v>61.8334</v>
       </c>
       <c r="F9" s="3">
         <v>4</v>
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="E10" s="10">
-        <v>58.8587</v>
+        <v>58.881</v>
       </c>
       <c r="F10" s="3">
         <v>2</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="E11" s="10">
-        <v>53.4891</v>
+        <v>53.4789</v>
       </c>
       <c r="F11" s="3">
         <v>12</v>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="E12" s="10">
-        <v>50.9062</v>
+        <v>50.9072</v>
       </c>
       <c r="F12" s="3">
         <v>11</v>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="E13" s="10">
-        <v>81.456</v>
+        <v>81.4563</v>
       </c>
       <c r="F13" s="3">
         <v>4</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="E14" s="10">
-        <v>66.361</v>
+        <v>66.351</v>
       </c>
       <c r="F14" s="3">
         <v>3</v>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="E15" s="10">
-        <v>53.0135</v>
+        <v>52.9869</v>
       </c>
       <c r="F15" s="3">
         <v>12</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="E16" s="10">
-        <v>51.1606</v>
+        <v>51.1597</v>
       </c>
       <c r="F16" s="3">
         <v>11</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="E17" s="10">
-        <v>46.5485</v>
+        <v>46.5748</v>
       </c>
       <c r="F17" s="3">
         <v>2</v>
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="E18" s="10">
-        <v>83.22620000000001</v>
+        <v>83.2371</v>
       </c>
       <c r="F18" s="3">
         <v>5</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="E19" s="10">
-        <v>67.5331</v>
+        <v>67.5321</v>
       </c>
       <c r="F19" s="3">
         <v>7</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="E20" s="10">
-        <v>55.9434</v>
+        <v>55.9425</v>
       </c>
       <c r="F20" s="3">
         <v>6</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="E21" s="10">
-        <v>50.8444</v>
+        <v>50.8848</v>
       </c>
       <c r="F21" s="3">
         <v>8</v>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="E22" s="10">
-        <v>45.1783</v>
+        <v>45.1546</v>
       </c>
       <c r="F22" s="3">
         <v>10</v>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="E23" s="10">
-        <v>88.2225</v>
+        <v>88.1905</v>
       </c>
       <c r="F23" s="3">
         <v>6</v>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E24" s="10">
-        <v>57.0211</v>
+        <v>57.0217</v>
       </c>
       <c r="F24" s="3">
         <v>7</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="E25" s="10">
-        <v>54.9134</v>
+        <v>54.9202</v>
       </c>
       <c r="F25" s="3">
         <v>5</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="E26" s="10">
-        <v>50.7811</v>
+        <v>50.829</v>
       </c>
       <c r="F26" s="3">
         <v>8</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="E27" s="10">
-        <v>44.3837</v>
+        <v>44.3945</v>
       </c>
       <c r="F27" s="3">
         <v>14</v>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="E28" s="10">
-        <v>80.224</v>
+        <v>80.22369999999999</v>
       </c>
       <c r="F28" s="3">
         <v>7</v>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="E29" s="10">
-        <v>61.9705</v>
+        <v>61.9704</v>
       </c>
       <c r="F29" s="3">
         <v>5</v>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="E30" s="10">
-        <v>56.0048</v>
+        <v>55.9789</v>
       </c>
       <c r="F30" s="3">
         <v>6</v>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="E31" s="10">
-        <v>52.9364</v>
+        <v>52.9681</v>
       </c>
       <c r="F31" s="3">
         <v>8</v>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="E32" s="10">
-        <v>49.2049</v>
+        <v>49.2026</v>
       </c>
       <c r="F32" s="3">
         <v>11</v>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="E33" s="10">
-        <v>62.9728</v>
+        <v>63.0171</v>
       </c>
       <c r="F33" s="3">
         <v>8</v>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="E34" s="10">
-        <v>46.8048</v>
+        <v>46.8044</v>
       </c>
       <c r="F34" s="3">
         <v>11</v>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="E35" s="10">
-        <v>40.9513</v>
+        <v>40.9511</v>
       </c>
       <c r="F35" s="3">
         <v>9</v>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="E36" s="10">
-        <v>38.3995</v>
+        <v>38.4411</v>
       </c>
       <c r="F36" s="3">
         <v>3</v>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="E37" s="10">
-        <v>38.0241</v>
+        <v>37.9898</v>
       </c>
       <c r="F37" s="3">
         <v>50</v>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="E38" s="10">
-        <v>79.96729999999999</v>
+        <v>79.967</v>
       </c>
       <c r="F38" s="3">
         <v>9</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="E39" s="10">
-        <v>48.3744</v>
+        <v>48.3706</v>
       </c>
       <c r="F39" s="3">
         <v>11</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="E40" s="10">
-        <v>44.682</v>
+        <v>44.6792</v>
       </c>
       <c r="F40" s="3">
         <v>15</v>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="E41" s="10">
-        <v>44.1424</v>
+        <v>44.1111</v>
       </c>
       <c r="F41" s="3">
         <v>3</v>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="E42" s="10">
-        <v>44.1401</v>
+        <v>44.0816</v>
       </c>
       <c r="F42" s="3">
         <v>13</v>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="E43" s="10">
-        <v>90.2171</v>
+        <v>90.17610000000001</v>
       </c>
       <c r="F43" s="3">
         <v>10</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E44" s="10">
-        <v>46.5989</v>
+        <v>46.6063</v>
       </c>
       <c r="F44" s="3">
         <v>5</v>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="E45" s="10">
-        <v>45.2599</v>
+        <v>45.2739</v>
       </c>
       <c r="F45" s="3">
         <v>8</v>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="E46" s="10">
-        <v>44.3804</v>
+        <v>44.3769</v>
       </c>
       <c r="F46" s="3">
         <v>11</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="E47" s="10">
-        <v>43.0331</v>
+        <v>43.0319</v>
       </c>
       <c r="F47" s="3">
         <v>51</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="E48" s="10">
-        <v>71.2756</v>
+        <v>71.2753</v>
       </c>
       <c r="F48" s="3">
         <v>11</v>
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="E49" s="10">
-        <v>62.5061</v>
+        <v>62.5247</v>
       </c>
       <c r="F49" s="3">
         <v>3</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="E50" s="10">
-        <v>58.1521</v>
+        <v>58.1827</v>
       </c>
       <c r="F50" s="3">
         <v>2</v>
@@ -10831,7 +10831,7 @@
         </is>
       </c>
       <c r="E51" s="10">
-        <v>49.6608</v>
+        <v>49.6597</v>
       </c>
       <c r="F51" s="3">
         <v>4</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="E52" s="10">
-        <v>47.8536</v>
+        <v>47.8525</v>
       </c>
       <c r="F52" s="3">
         <v>12</v>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="E53" s="10">
-        <v>75.1172</v>
+        <v>75.1169</v>
       </c>
       <c r="F53" s="3">
         <v>12</v>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="E54" s="10">
-        <v>61.7782</v>
+        <v>61.7781</v>
       </c>
       <c r="F54" s="3">
         <v>4</v>
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="E55" s="10">
-        <v>60.2447</v>
+        <v>60.2347</v>
       </c>
       <c r="F55" s="3">
         <v>3</v>
@@ -11526,7 +11526,7 @@
         </is>
       </c>
       <c r="E56" s="10">
-        <v>56.335</v>
+        <v>56.3346</v>
       </c>
       <c r="F56" s="3">
         <v>11</v>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="E57" s="10">
-        <v>54.3693</v>
+        <v>54.3917</v>
       </c>
       <c r="F57" s="3">
         <v>2</v>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="E58" s="10">
-        <v>76.4391</v>
+        <v>76.386</v>
       </c>
       <c r="F58" s="3">
         <v>13</v>
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="E59" s="10">
-        <v>48.5378</v>
+        <v>48.5384</v>
       </c>
       <c r="F59" s="3">
         <v>4</v>
@@ -12082,7 +12082,7 @@
         </is>
       </c>
       <c r="E60" s="10">
-        <v>46.2296</v>
+        <v>46.2295</v>
       </c>
       <c r="F60" s="3">
         <v>9</v>
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="E61" s="10">
-        <v>45.3985</v>
+        <v>45.3994</v>
       </c>
       <c r="F61" s="3">
         <v>11</v>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="E62" s="10">
-        <v>45.0099</v>
+        <v>44.9964</v>
       </c>
       <c r="F62" s="3">
         <v>3</v>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="E63" s="10">
-        <v>81.53879999999999</v>
+        <v>81.54640000000001</v>
       </c>
       <c r="F63" s="3">
         <v>14</v>
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="E64" s="10">
-        <v>48.6977</v>
+        <v>48.6954</v>
       </c>
       <c r="F64" s="3">
         <v>11</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="E65" s="10">
-        <v>47.8543</v>
+        <v>47.8716</v>
       </c>
       <c r="F65" s="3">
         <v>5</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="E66" s="10">
-        <v>47.4447</v>
+        <v>47.3984</v>
       </c>
       <c r="F66" s="3">
         <v>6</v>
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="E67" s="10">
-        <v>45.2609</v>
+        <v>45.2601</v>
       </c>
       <c r="F67" s="3">
         <v>7</v>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="E68" s="10">
-        <v>83.0355</v>
+        <v>83.036</v>
       </c>
       <c r="F68" s="3">
         <v>15</v>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="E69" s="10">
-        <v>47.3492</v>
+        <v>47.3501</v>
       </c>
       <c r="F69" s="3">
         <v>11</v>
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="E70" s="10">
-        <v>45.3413</v>
+        <v>45.3418</v>
       </c>
       <c r="F70" s="3">
         <v>9</v>
@@ -13611,7 +13611,7 @@
         </is>
       </c>
       <c r="E71" s="10">
-        <v>43.4386</v>
+        <v>43.4845</v>
       </c>
       <c r="F71" s="3">
         <v>8</v>
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="E72" s="10">
-        <v>42.2831</v>
+        <v>42.2701</v>
       </c>
       <c r="F72" s="3">
         <v>3</v>
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="E73" s="10">
-        <v>76.2634</v>
+        <v>76.3137</v>
       </c>
       <c r="F73" s="3">
         <v>16</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E74" s="10">
-        <v>41.123</v>
+        <v>41.1236</v>
       </c>
       <c r="F74" s="3">
         <v>42</v>
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="E75" s="10">
-        <v>40.9642</v>
+        <v>40.8847</v>
       </c>
       <c r="F75" s="3">
         <v>37</v>
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="E76" s="10">
-        <v>40.0292</v>
+        <v>40.0301</v>
       </c>
       <c r="F76" s="3">
         <v>40</v>
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="E77" s="10">
-        <v>38.6154</v>
+        <v>38.6158</v>
       </c>
       <c r="F77" s="3">
         <v>49</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="E78" s="10">
-        <v>49.6548</v>
+        <v>49.6748</v>
       </c>
       <c r="F78" s="3">
         <v>13</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="E79" s="10">
-        <v>47.5099</v>
+        <v>47.5149</v>
       </c>
       <c r="F79" s="3">
         <v>45</v>
@@ -14862,7 +14862,7 @@
         </is>
       </c>
       <c r="E80" s="10">
-        <v>47.4222</v>
+        <v>47.4236</v>
       </c>
       <c r="F80" s="3">
         <v>32</v>
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="E81" s="10">
-        <v>47.2629</v>
+        <v>47.2648</v>
       </c>
       <c r="F81" s="3">
         <v>47</v>
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="E82" s="10">
-        <v>47.2503</v>
+        <v>47.252</v>
       </c>
       <c r="F82" s="3">
         <v>33</v>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="E83" s="10">
-        <v>38.8251</v>
+        <v>38.9282</v>
       </c>
       <c r="F83" s="3">
         <v>6</v>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="E84" s="10">
-        <v>37.5291</v>
+        <v>37.5251</v>
       </c>
       <c r="F84" s="3">
         <v>2</v>
@@ -15557,7 +15557,7 @@
         </is>
       </c>
       <c r="E85" s="10">
-        <v>37.2504</v>
+        <v>37.2388</v>
       </c>
       <c r="F85" s="3">
         <v>48</v>
@@ -15696,7 +15696,7 @@
         </is>
       </c>
       <c r="E86" s="10">
-        <v>36.6572</v>
+        <v>36.6563</v>
       </c>
       <c r="F86" s="3">
         <v>41</v>
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="E87" s="10">
-        <v>36.4548</v>
+        <v>36.4538</v>
       </c>
       <c r="F87" s="3">
         <v>18</v>
@@ -15974,7 +15974,7 @@
         </is>
       </c>
       <c r="E88" s="10">
-        <v>48.4937</v>
+        <v>48.4922</v>
       </c>
       <c r="F88" s="3">
         <v>11</v>
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="E89" s="10">
-        <v>46.3895</v>
+        <v>46.3878</v>
       </c>
       <c r="F89" s="3">
         <v>4</v>
@@ -16252,7 +16252,7 @@
         </is>
       </c>
       <c r="E90" s="10">
-        <v>45.3643</v>
+        <v>45.3976</v>
       </c>
       <c r="F90" s="3">
         <v>3</v>
@@ -16391,7 +16391,7 @@
         </is>
       </c>
       <c r="E91" s="10">
-        <v>42.9353</v>
+        <v>42.8702</v>
       </c>
       <c r="F91" s="3">
         <v>6</v>
@@ -16530,7 +16530,7 @@
         </is>
       </c>
       <c r="E92" s="10">
-        <v>42.8262</v>
+        <v>42.8154</v>
       </c>
       <c r="F92" s="3">
         <v>12</v>
@@ -16808,7 +16808,7 @@
         </is>
       </c>
       <c r="E94" s="10">
-        <v>41.9215</v>
+        <v>41.9197</v>
       </c>
       <c r="F94" s="3">
         <v>11</v>
@@ -16947,7 +16947,7 @@
         </is>
       </c>
       <c r="E95" s="10">
-        <v>40.4532</v>
+        <v>40.4479</v>
       </c>
       <c r="F95" s="3">
         <v>5</v>
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="E96" s="10">
-        <v>38.1341</v>
+        <v>38.1324</v>
       </c>
       <c r="F96" s="3">
         <v>15</v>
@@ -17225,7 +17225,7 @@
         </is>
       </c>
       <c r="E97" s="10">
-        <v>38.0809</v>
+        <v>38.1266</v>
       </c>
       <c r="F97" s="3">
         <v>8</v>
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="E98" s="10">
-        <v>58.4443</v>
+        <v>58.4431</v>
       </c>
       <c r="F98" s="3">
         <v>47</v>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="E99" s="10">
-        <v>58.3089</v>
+        <v>58.3077</v>
       </c>
       <c r="F99" s="3">
         <v>41</v>
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="E100" s="10">
-        <v>58.0754</v>
+        <v>58.06</v>
       </c>
       <c r="F100" s="3">
         <v>48</v>
@@ -17781,7 +17781,7 @@
         </is>
       </c>
       <c r="E101" s="10">
-        <v>57.7999</v>
+        <v>57.8179</v>
       </c>
       <c r="F101" s="3">
         <v>17</v>
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="E102" s="10">
-        <v>57.4258</v>
+        <v>57.4247</v>
       </c>
       <c r="F102" s="3">
         <v>18</v>
@@ -18161,7 +18161,7 @@
         </is>
       </c>
       <c r="H3" s="4">
-        <v>46290.99182502231</v>
+        <v>46292.52817064675</v>
       </c>
     </row>
     <row r="4">
@@ -18195,7 +18195,7 @@
         </is>
       </c>
       <c r="H4" s="4">
-        <v>46290.991825282</v>
+        <v>46292.52817096916</v>
       </c>
     </row>
   </sheetData>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="Q3" s="10">
-        <v>48.4937</v>
+        <v>48.4922</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="S3" s="4">
-        <v>46290.991825282</v>
+        <v>46292.52817096916</v>
       </c>
     </row>
   </sheetData>
